--- a/artfynd/A 27265-2020 artfynd.xlsx
+++ b/artfynd/A 27265-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27265-2020 artfynd.xlsx
+++ b/artfynd/A 27265-2020 artfynd.xlsx
@@ -2156,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117734844</v>
+        <v>117734827</v>
       </c>
       <c r="B16" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387955</v>
+        <v>387528</v>
       </c>
       <c r="R16" t="n">
-        <v>6715366</v>
+        <v>6715155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117734848</v>
+        <v>117734844</v>
       </c>
       <c r="B17" t="n">
-        <v>82259</v>
+        <v>78514</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387823</v>
+        <v>387955</v>
       </c>
       <c r="R17" t="n">
-        <v>6715333</v>
+        <v>6715366</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,7 +2342,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2361,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117734827</v>
+        <v>117734848</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>82259</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,21 +2376,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,10 +2400,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387528</v>
+        <v>387823</v>
       </c>
       <c r="R18" t="n">
-        <v>6715155</v>
+        <v>6715333</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,6 +2444,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117734853</v>
+        <v>117734839</v>
       </c>
       <c r="B21" t="n">
-        <v>90464</v>
+        <v>79098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,25 +2679,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387783</v>
+        <v>388487</v>
       </c>
       <c r="R21" t="n">
-        <v>6715342</v>
+        <v>6715901</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117734839</v>
+        <v>117734853</v>
       </c>
       <c r="B22" t="n">
-        <v>79098</v>
+        <v>90464</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>388487</v>
+        <v>387783</v>
       </c>
       <c r="R22" t="n">
-        <v>6715901</v>
+        <v>6715342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117734851</v>
+        <v>117734838</v>
       </c>
       <c r="B25" t="n">
-        <v>97740</v>
+        <v>86816</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,25 +3087,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220093</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387802</v>
+        <v>388524</v>
       </c>
       <c r="R25" t="n">
-        <v>6715191</v>
+        <v>6715944</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117734838</v>
+        <v>117734851</v>
       </c>
       <c r="B27" t="n">
-        <v>86816</v>
+        <v>97740</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3291,25 +3291,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>220093</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>388524</v>
+        <v>387802</v>
       </c>
       <c r="R27" t="n">
-        <v>6715944</v>
+        <v>6715191</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117734855</v>
+        <v>117734837</v>
       </c>
       <c r="B29" t="n">
-        <v>74531</v>
+        <v>80437</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3495,41 +3495,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387718</v>
+        <v>388550</v>
       </c>
       <c r="R29" t="n">
-        <v>6715282</v>
+        <v>6715951</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3570,7 +3567,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3589,10 +3585,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117734837</v>
+        <v>117734855</v>
       </c>
       <c r="B30" t="n">
-        <v>80437</v>
+        <v>74531</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3601,38 +3597,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>388550</v>
+        <v>387718</v>
       </c>
       <c r="R30" t="n">
-        <v>6715951</v>
+        <v>6715282</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,6 +3672,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27265-2020 artfynd.xlsx
+++ b/artfynd/A 27265-2020 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117734824</v>
+        <v>117734841</v>
       </c>
       <c r="B4" t="n">
-        <v>90464</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388394</v>
+        <v>388211</v>
       </c>
       <c r="R4" t="n">
-        <v>6715770</v>
+        <v>6715684</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117734841</v>
+        <v>117734824</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>90464</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388211</v>
+        <v>388394</v>
       </c>
       <c r="R5" t="n">
-        <v>6715684</v>
+        <v>6715770</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117743429</v>
+        <v>117743127</v>
       </c>
       <c r="B6" t="n">
         <v>78514</v>
@@ -1139,14 +1139,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
+          <t>Ackberget, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388443</v>
+        <v>388234</v>
       </c>
       <c r="R6" t="n">
-        <v>6715850</v>
+        <v>6715683</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117743130</v>
+        <v>117743129</v>
       </c>
       <c r="B7" t="n">
-        <v>86816</v>
+        <v>78514</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388415</v>
+        <v>388236</v>
       </c>
       <c r="R7" t="n">
-        <v>6715788</v>
+        <v>6715717</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117743132</v>
+        <v>117743130</v>
       </c>
       <c r="B8" t="n">
-        <v>78217</v>
+        <v>86816</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388628</v>
+        <v>388415</v>
       </c>
       <c r="R8" t="n">
-        <v>6715839</v>
+        <v>6715788</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117743133</v>
+        <v>117743429</v>
       </c>
       <c r="B9" t="n">
         <v>78514</v>
@@ -1445,14 +1445,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ackberget, Vrm</t>
+          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388313</v>
+        <v>388443</v>
       </c>
       <c r="R9" t="n">
-        <v>6715659</v>
+        <v>6715850</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,22 +1499,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117743131</v>
+        <v>117743132</v>
       </c>
       <c r="B10" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117743129</v>
+        <v>117743133</v>
       </c>
       <c r="B12" t="n">
         <v>78514</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388236</v>
+        <v>388313</v>
       </c>
       <c r="R12" t="n">
-        <v>6715717</v>
+        <v>6715659</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117743127</v>
+        <v>117743131</v>
       </c>
       <c r="B13" t="n">
-        <v>78514</v>
+        <v>78216</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388234</v>
+        <v>388628</v>
       </c>
       <c r="R13" t="n">
-        <v>6715683</v>
+        <v>6715839</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117734827</v>
+        <v>117734837</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>80437</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387528</v>
+        <v>388550</v>
       </c>
       <c r="R16" t="n">
-        <v>6715155</v>
+        <v>6715951</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117734844</v>
+        <v>117734867</v>
       </c>
       <c r="B17" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387955</v>
+        <v>387481</v>
       </c>
       <c r="R17" t="n">
-        <v>6715366</v>
+        <v>6715122</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117734848</v>
+        <v>117734838</v>
       </c>
       <c r="B18" t="n">
-        <v>82259</v>
+        <v>86816</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2376,21 +2376,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387823</v>
+        <v>388524</v>
       </c>
       <c r="R18" t="n">
-        <v>6715333</v>
+        <v>6715944</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,7 +2444,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2463,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117734849</v>
+        <v>117734853</v>
       </c>
       <c r="B19" t="n">
-        <v>97857</v>
+        <v>90464</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2503,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387821</v>
+        <v>387783</v>
       </c>
       <c r="R19" t="n">
-        <v>6715345</v>
+        <v>6715342</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,10 +2564,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117734854</v>
+        <v>117734839</v>
       </c>
       <c r="B20" t="n">
-        <v>74531</v>
+        <v>79098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,25 +2576,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2605,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387749</v>
+        <v>388487</v>
       </c>
       <c r="R20" t="n">
-        <v>6715306</v>
+        <v>6715901</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,10 +2666,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117734839</v>
+        <v>117734844</v>
       </c>
       <c r="B21" t="n">
-        <v>79098</v>
+        <v>78514</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2683,21 +2682,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2707,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>388487</v>
+        <v>387955</v>
       </c>
       <c r="R21" t="n">
-        <v>6715901</v>
+        <v>6715366</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,10 +2768,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117734853</v>
+        <v>117734859</v>
       </c>
       <c r="B22" t="n">
-        <v>90464</v>
+        <v>74531</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2785,21 +2784,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2809,10 +2808,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387783</v>
+        <v>387706</v>
       </c>
       <c r="R22" t="n">
-        <v>6715342</v>
+        <v>6715260</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,10 +2870,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117734868</v>
+        <v>117734851</v>
       </c>
       <c r="B23" t="n">
-        <v>78514</v>
+        <v>97740</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,25 +2882,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2911,10 +2910,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>387438</v>
+        <v>387802</v>
       </c>
       <c r="R23" t="n">
-        <v>6715052</v>
+        <v>6715191</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117734846</v>
+        <v>117734864</v>
       </c>
       <c r="B24" t="n">
-        <v>74531</v>
+        <v>78480</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,25 +2984,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3013,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387836</v>
+        <v>387609</v>
       </c>
       <c r="R24" t="n">
-        <v>6715344</v>
+        <v>6715212</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,10 +3074,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117734838</v>
+        <v>117734845</v>
       </c>
       <c r="B25" t="n">
-        <v>86816</v>
+        <v>74531</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,25 +3086,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3115,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>388524</v>
+        <v>387873</v>
       </c>
       <c r="R25" t="n">
-        <v>6715944</v>
+        <v>6715327</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3177,10 +3176,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117734847</v>
+        <v>117734849</v>
       </c>
       <c r="B26" t="n">
-        <v>74531</v>
+        <v>97857</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3193,21 +3192,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3217,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387824</v>
+        <v>387821</v>
       </c>
       <c r="R26" t="n">
-        <v>6715352</v>
+        <v>6715345</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3279,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117734851</v>
+        <v>117734857</v>
       </c>
       <c r="B27" t="n">
-        <v>97740</v>
+        <v>78643</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3291,25 +3290,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220093</v>
+        <v>1249</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3319,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387802</v>
+        <v>387718</v>
       </c>
       <c r="R27" t="n">
-        <v>6715191</v>
+        <v>6715297</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3381,10 +3380,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117734840</v>
+        <v>117734827</v>
       </c>
       <c r="B28" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3397,21 +3396,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3421,10 +3420,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>388487</v>
+        <v>387528</v>
       </c>
       <c r="R28" t="n">
-        <v>6715902</v>
+        <v>6715155</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3483,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117734837</v>
+        <v>117734852</v>
       </c>
       <c r="B29" t="n">
-        <v>80437</v>
+        <v>97740</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3495,25 +3494,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>220093</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3523,10 +3522,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>388550</v>
+        <v>387792</v>
       </c>
       <c r="R29" t="n">
-        <v>6715951</v>
+        <v>6715346</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,10 +3584,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117734855</v>
+        <v>117734862</v>
       </c>
       <c r="B30" t="n">
-        <v>74531</v>
+        <v>78480</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3597,41 +3596,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387718</v>
+        <v>387694</v>
       </c>
       <c r="R30" t="n">
-        <v>6715282</v>
+        <v>6715131</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,7 +3668,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3691,7 +3686,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117734850</v>
+        <v>117734843</v>
       </c>
       <c r="B31" t="n">
         <v>78480</v>
@@ -3731,10 +3726,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387812</v>
+        <v>387985</v>
       </c>
       <c r="R31" t="n">
-        <v>6715184</v>
+        <v>6715351</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3793,7 +3788,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117734867</v>
+        <v>117734850</v>
       </c>
       <c r="B32" t="n">
         <v>78480</v>
@@ -3833,10 +3828,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387481</v>
+        <v>387812</v>
       </c>
       <c r="R32" t="n">
-        <v>6715122</v>
+        <v>6715184</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3895,10 +3890,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117734845</v>
+        <v>117734840</v>
       </c>
       <c r="B33" t="n">
-        <v>74531</v>
+        <v>78217</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3907,25 +3902,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3935,10 +3930,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387873</v>
+        <v>388487</v>
       </c>
       <c r="R33" t="n">
-        <v>6715327</v>
+        <v>6715902</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3997,10 +3992,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117734862</v>
+        <v>117734847</v>
       </c>
       <c r="B34" t="n">
-        <v>78480</v>
+        <v>74531</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4009,25 +4004,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4037,10 +4032,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387694</v>
+        <v>387824</v>
       </c>
       <c r="R34" t="n">
-        <v>6715131</v>
+        <v>6715352</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4099,10 +4094,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117734858</v>
+        <v>117734848</v>
       </c>
       <c r="B35" t="n">
-        <v>97857</v>
+        <v>82259</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4111,25 +4106,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4139,10 +4134,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>387713</v>
+        <v>387823</v>
       </c>
       <c r="R35" t="n">
-        <v>6715276</v>
+        <v>6715333</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,6 +4178,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4201,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117734859</v>
+        <v>117734868</v>
       </c>
       <c r="B36" t="n">
-        <v>74531</v>
+        <v>78514</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4213,25 +4209,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4241,10 +4237,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>387706</v>
+        <v>387438</v>
       </c>
       <c r="R36" t="n">
-        <v>6715260</v>
+        <v>6715052</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4303,10 +4299,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117734843</v>
+        <v>117734858</v>
       </c>
       <c r="B37" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4315,25 +4311,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4343,10 +4339,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387985</v>
+        <v>387713</v>
       </c>
       <c r="R37" t="n">
-        <v>6715351</v>
+        <v>6715276</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4405,10 +4401,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117734864</v>
+        <v>117734846</v>
       </c>
       <c r="B38" t="n">
-        <v>78480</v>
+        <v>74531</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4417,25 +4413,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4445,10 +4441,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387609</v>
+        <v>387836</v>
       </c>
       <c r="R38" t="n">
-        <v>6715212</v>
+        <v>6715344</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4507,10 +4503,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117734863</v>
+        <v>117734855</v>
       </c>
       <c r="B39" t="n">
-        <v>97740</v>
+        <v>74531</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4523,34 +4519,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220093</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387659</v>
+        <v>387718</v>
       </c>
       <c r="R39" t="n">
-        <v>6715262</v>
+        <v>6715282</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,6 +4590,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4609,7 +4609,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117734852</v>
+        <v>117734863</v>
       </c>
       <c r="B40" t="n">
         <v>97740</v>
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387792</v>
+        <v>387659</v>
       </c>
       <c r="R40" t="n">
-        <v>6715346</v>
+        <v>6715262</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117734866</v>
+        <v>117734854</v>
       </c>
       <c r="B41" t="n">
-        <v>97740</v>
+        <v>74531</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220093</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387512</v>
+        <v>387749</v>
       </c>
       <c r="R41" t="n">
-        <v>6715088</v>
+        <v>6715306</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4813,10 +4813,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117734857</v>
+        <v>117734866</v>
       </c>
       <c r="B42" t="n">
-        <v>78643</v>
+        <v>97740</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4825,25 +4825,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1249</v>
+        <v>220093</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387718</v>
+        <v>387512</v>
       </c>
       <c r="R42" t="n">
-        <v>6715297</v>
+        <v>6715088</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117743434</v>
+        <v>117743126</v>
       </c>
       <c r="B43" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4927,38 +4927,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
+          <t>Ackberget, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>388196</v>
+        <v>388116</v>
       </c>
       <c r="R43" t="n">
-        <v>6715751</v>
+        <v>6715350</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5005,22 +5005,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117743134</v>
+        <v>117743114</v>
       </c>
       <c r="B44" t="n">
-        <v>97740</v>
+        <v>78480</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5029,25 +5029,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387804</v>
+        <v>387423</v>
       </c>
       <c r="R44" t="n">
-        <v>6715171</v>
+        <v>6715019</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5119,10 +5119,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117743436</v>
+        <v>117743434</v>
       </c>
       <c r="B45" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387837</v>
+        <v>388196</v>
       </c>
       <c r="R45" t="n">
-        <v>6715375</v>
+        <v>6715751</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,7 +5221,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117743123</v>
+        <v>117743436</v>
       </c>
       <c r="B46" t="n">
         <v>97857</v>
@@ -5257,14 +5257,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ackberget, Vrm</t>
+          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387825</v>
+        <v>387837</v>
       </c>
       <c r="R46" t="n">
-        <v>6715329</v>
+        <v>6715375</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5311,22 +5311,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117743116</v>
+        <v>117743430</v>
       </c>
       <c r="B47" t="n">
-        <v>97740</v>
+        <v>97857</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5339,34 +5339,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ackberget, Vrm</t>
+          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387447</v>
+        <v>387840</v>
       </c>
       <c r="R47" t="n">
-        <v>6715085</v>
+        <v>6715333</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5413,22 +5413,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117743121</v>
+        <v>117743115</v>
       </c>
       <c r="B48" t="n">
-        <v>78480</v>
+        <v>97740</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5437,25 +5437,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387719</v>
+        <v>387463</v>
       </c>
       <c r="R48" t="n">
-        <v>6715279</v>
+        <v>6715077</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117743120</v>
+        <v>117743124</v>
       </c>
       <c r="B49" t="n">
-        <v>97857</v>
+        <v>97740</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387727</v>
+        <v>387864</v>
       </c>
       <c r="R49" t="n">
-        <v>6715238</v>
+        <v>6715291</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5629,7 +5629,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117743430</v>
+        <v>117743120</v>
       </c>
       <c r="B50" t="n">
         <v>97857</v>
@@ -5665,14 +5665,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
+          <t>Ackberget, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>387840</v>
+        <v>387727</v>
       </c>
       <c r="R50" t="n">
-        <v>6715333</v>
+        <v>6715238</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5719,19 +5719,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117743114</v>
+        <v>117743121</v>
       </c>
       <c r="B51" t="n">
         <v>78480</v>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>387423</v>
+        <v>387719</v>
       </c>
       <c r="R51" t="n">
-        <v>6715019</v>
+        <v>6715279</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5833,10 +5833,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117743119</v>
+        <v>117743125</v>
       </c>
       <c r="B52" t="n">
-        <v>97857</v>
+        <v>97740</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5849,21 +5849,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5873,10 +5873,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>387713</v>
+        <v>388061</v>
       </c>
       <c r="R52" t="n">
-        <v>6715228</v>
+        <v>6715307</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5935,10 +5935,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117743115</v>
+        <v>117743117</v>
       </c>
       <c r="B53" t="n">
-        <v>97740</v>
+        <v>78125</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5947,25 +5947,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220093</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387463</v>
+        <v>387578</v>
       </c>
       <c r="R53" t="n">
-        <v>6715077</v>
+        <v>6715145</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6037,10 +6037,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117743117</v>
+        <v>117743116</v>
       </c>
       <c r="B54" t="n">
-        <v>78125</v>
+        <v>97740</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6049,25 +6049,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>220093</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6077,10 +6077,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387578</v>
+        <v>387447</v>
       </c>
       <c r="R54" t="n">
-        <v>6715145</v>
+        <v>6715085</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6139,10 +6139,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117743118</v>
+        <v>117743119</v>
       </c>
       <c r="B55" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6151,25 +6151,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387669</v>
+        <v>387713</v>
       </c>
       <c r="R55" t="n">
-        <v>6715247</v>
+        <v>6715228</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117743125</v>
+        <v>117743134</v>
       </c>
       <c r="B57" t="n">
         <v>97740</v>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>388061</v>
+        <v>387804</v>
       </c>
       <c r="R57" t="n">
-        <v>6715307</v>
+        <v>6715171</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117743126</v>
+        <v>117743118</v>
       </c>
       <c r="B58" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6470,25 +6470,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>388116</v>
+        <v>387669</v>
       </c>
       <c r="R58" t="n">
-        <v>6715350</v>
+        <v>6715247</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6560,10 +6560,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117743124</v>
+        <v>117743123</v>
       </c>
       <c r="B59" t="n">
-        <v>97740</v>
+        <v>97857</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>387864</v>
+        <v>387825</v>
       </c>
       <c r="R59" t="n">
-        <v>6715291</v>
+        <v>6715329</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 27265-2020 artfynd.xlsx
+++ b/artfynd/A 27265-2020 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>117734841</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>117734824</v>
       </c>
       <c r="B5" t="n">
-        <v>90464</v>
+        <v>90466</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117743127</v>
+        <v>117743433</v>
       </c>
       <c r="B6" t="n">
-        <v>78514</v>
+        <v>86818</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,34 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ackberget, Vrm</t>
+          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388234</v>
+        <v>388393</v>
       </c>
       <c r="R6" t="n">
-        <v>6715683</v>
+        <v>6715758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117743129</v>
+        <v>117743127</v>
       </c>
       <c r="B7" t="n">
-        <v>78514</v>
+        <v>78516</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388236</v>
+        <v>388234</v>
       </c>
       <c r="R7" t="n">
-        <v>6715717</v>
+        <v>6715683</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117743130</v>
+        <v>117743129</v>
       </c>
       <c r="B8" t="n">
-        <v>86816</v>
+        <v>78516</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388415</v>
+        <v>388236</v>
       </c>
       <c r="R8" t="n">
-        <v>6715788</v>
+        <v>6715717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117743429</v>
+        <v>117743130</v>
       </c>
       <c r="B9" t="n">
-        <v>78514</v>
+        <v>86818</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
+          <t>Ackberget, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388443</v>
+        <v>388415</v>
       </c>
       <c r="R9" t="n">
-        <v>6715850</v>
+        <v>6715788</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,22 +1499,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117743132</v>
+        <v>117743133</v>
       </c>
       <c r="B10" t="n">
-        <v>78217</v>
+        <v>78516</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388628</v>
+        <v>388313</v>
       </c>
       <c r="R10" t="n">
-        <v>6715839</v>
+        <v>6715659</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117743433</v>
+        <v>117743429</v>
       </c>
       <c r="B11" t="n">
-        <v>86816</v>
+        <v>78516</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388393</v>
+        <v>388443</v>
       </c>
       <c r="R11" t="n">
-        <v>6715758</v>
+        <v>6715850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117743133</v>
+        <v>117743132</v>
       </c>
       <c r="B12" t="n">
-        <v>78514</v>
+        <v>78219</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388313</v>
+        <v>388628</v>
       </c>
       <c r="R12" t="n">
-        <v>6715659</v>
+        <v>6715839</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
         <v>117743131</v>
       </c>
       <c r="B13" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117734837</v>
+        <v>117734857</v>
       </c>
       <c r="B16" t="n">
-        <v>80437</v>
+        <v>78645</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2168,25 +2168,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>1249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388550</v>
+        <v>387718</v>
       </c>
       <c r="R16" t="n">
-        <v>6715951</v>
+        <v>6715297</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117734867</v>
+        <v>117734858</v>
       </c>
       <c r="B17" t="n">
-        <v>78480</v>
+        <v>97859</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2270,25 +2270,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387481</v>
+        <v>387713</v>
       </c>
       <c r="R17" t="n">
-        <v>6715122</v>
+        <v>6715276</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117734838</v>
+        <v>117734849</v>
       </c>
       <c r="B18" t="n">
-        <v>86816</v>
+        <v>97859</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2372,25 +2372,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388524</v>
+        <v>387821</v>
       </c>
       <c r="R18" t="n">
-        <v>6715944</v>
+        <v>6715345</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117734853</v>
+        <v>117734847</v>
       </c>
       <c r="B19" t="n">
-        <v>90464</v>
+        <v>74533</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387783</v>
+        <v>387824</v>
       </c>
       <c r="R19" t="n">
-        <v>6715342</v>
+        <v>6715352</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117734839</v>
+        <v>117734862</v>
       </c>
       <c r="B20" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>388487</v>
+        <v>387694</v>
       </c>
       <c r="R20" t="n">
-        <v>6715901</v>
+        <v>6715131</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117734844</v>
+        <v>117734850</v>
       </c>
       <c r="B21" t="n">
-        <v>78514</v>
+        <v>78482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387955</v>
+        <v>387812</v>
       </c>
       <c r="R21" t="n">
-        <v>6715366</v>
+        <v>6715184</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117734859</v>
+        <v>117734843</v>
       </c>
       <c r="B22" t="n">
-        <v>74531</v>
+        <v>78482</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2780,25 +2780,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387706</v>
+        <v>387985</v>
       </c>
       <c r="R22" t="n">
-        <v>6715260</v>
+        <v>6715351</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,10 +2870,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117734851</v>
+        <v>117734867</v>
       </c>
       <c r="B23" t="n">
-        <v>97740</v>
+        <v>78482</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2882,25 +2882,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>387802</v>
+        <v>387481</v>
       </c>
       <c r="R23" t="n">
-        <v>6715191</v>
+        <v>6715122</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117734864</v>
+        <v>117734854</v>
       </c>
       <c r="B24" t="n">
-        <v>78480</v>
+        <v>74533</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2984,25 +2984,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387609</v>
+        <v>387749</v>
       </c>
       <c r="R24" t="n">
-        <v>6715212</v>
+        <v>6715306</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117734845</v>
+        <v>117734827</v>
       </c>
       <c r="B25" t="n">
-        <v>74531</v>
+        <v>78482</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387873</v>
+        <v>387528</v>
       </c>
       <c r="R25" t="n">
-        <v>6715327</v>
+        <v>6715155</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,10 +3176,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117734849</v>
+        <v>117734863</v>
       </c>
       <c r="B26" t="n">
-        <v>97857</v>
+        <v>97742</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3192,21 +3192,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387821</v>
+        <v>387659</v>
       </c>
       <c r="R26" t="n">
-        <v>6715345</v>
+        <v>6715262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117734857</v>
+        <v>117734845</v>
       </c>
       <c r="B27" t="n">
-        <v>78643</v>
+        <v>74533</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3290,25 +3290,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1249</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387718</v>
+        <v>387873</v>
       </c>
       <c r="R27" t="n">
-        <v>6715297</v>
+        <v>6715327</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3380,10 +3380,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117734827</v>
+        <v>117734837</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>80439</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3396,21 +3396,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387528</v>
+        <v>388550</v>
       </c>
       <c r="R28" t="n">
-        <v>6715155</v>
+        <v>6715951</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117734852</v>
+        <v>117734844</v>
       </c>
       <c r="B29" t="n">
-        <v>97740</v>
+        <v>78516</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3494,25 +3494,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387792</v>
+        <v>387955</v>
       </c>
       <c r="R29" t="n">
-        <v>6715346</v>
+        <v>6715366</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117734862</v>
+        <v>117734852</v>
       </c>
       <c r="B30" t="n">
-        <v>78480</v>
+        <v>97742</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3596,25 +3596,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387694</v>
+        <v>387792</v>
       </c>
       <c r="R30" t="n">
-        <v>6715131</v>
+        <v>6715346</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117734843</v>
+        <v>117734864</v>
       </c>
       <c r="B31" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387985</v>
+        <v>387609</v>
       </c>
       <c r="R31" t="n">
-        <v>6715351</v>
+        <v>6715212</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117734850</v>
+        <v>117734859</v>
       </c>
       <c r="B32" t="n">
-        <v>78480</v>
+        <v>74533</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3800,25 +3800,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387812</v>
+        <v>387706</v>
       </c>
       <c r="R32" t="n">
-        <v>6715184</v>
+        <v>6715260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117734840</v>
+        <v>117734866</v>
       </c>
       <c r="B33" t="n">
-        <v>78217</v>
+        <v>97742</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3902,25 +3902,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>220093</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>388487</v>
+        <v>387512</v>
       </c>
       <c r="R33" t="n">
-        <v>6715902</v>
+        <v>6715088</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,10 +3992,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117734847</v>
+        <v>117734839</v>
       </c>
       <c r="B34" t="n">
-        <v>74531</v>
+        <v>79100</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4004,25 +4004,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387824</v>
+        <v>388487</v>
       </c>
       <c r="R34" t="n">
-        <v>6715352</v>
+        <v>6715901</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117734848</v>
+        <v>117734855</v>
       </c>
       <c r="B35" t="n">
-        <v>82259</v>
+        <v>74533</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4106,38 +4106,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6426</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>387823</v>
+        <v>387718</v>
       </c>
       <c r="R35" t="n">
-        <v>6715333</v>
+        <v>6715282</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4197,10 +4200,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117734868</v>
+        <v>117734851</v>
       </c>
       <c r="B36" t="n">
-        <v>78514</v>
+        <v>97742</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4209,25 +4212,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4237,10 +4240,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>387438</v>
+        <v>387802</v>
       </c>
       <c r="R36" t="n">
-        <v>6715052</v>
+        <v>6715191</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4299,10 +4302,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117734858</v>
+        <v>117734838</v>
       </c>
       <c r="B37" t="n">
-        <v>97857</v>
+        <v>86818</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4311,25 +4314,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4339,10 +4342,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387713</v>
+        <v>388524</v>
       </c>
       <c r="R37" t="n">
-        <v>6715276</v>
+        <v>6715944</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4401,10 +4404,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117734846</v>
+        <v>117734868</v>
       </c>
       <c r="B38" t="n">
-        <v>74531</v>
+        <v>78516</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4413,25 +4416,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4441,10 +4444,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387836</v>
+        <v>387438</v>
       </c>
       <c r="R38" t="n">
-        <v>6715344</v>
+        <v>6715052</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4503,10 +4506,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117734855</v>
+        <v>117734846</v>
       </c>
       <c r="B39" t="n">
-        <v>74531</v>
+        <v>74533</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4537,19 +4540,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387718</v>
+        <v>387836</v>
       </c>
       <c r="R39" t="n">
-        <v>6715282</v>
+        <v>6715344</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4590,7 +4590,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4609,10 +4608,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117734863</v>
+        <v>117734853</v>
       </c>
       <c r="B40" t="n">
-        <v>97740</v>
+        <v>90466</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4625,21 +4624,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220093</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4649,10 +4648,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387659</v>
+        <v>387783</v>
       </c>
       <c r="R40" t="n">
-        <v>6715262</v>
+        <v>6715342</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4711,10 +4710,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117734854</v>
+        <v>117734848</v>
       </c>
       <c r="B41" t="n">
-        <v>74531</v>
+        <v>82261</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4723,25 +4722,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4751,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387749</v>
+        <v>387823</v>
       </c>
       <c r="R41" t="n">
-        <v>6715306</v>
+        <v>6715333</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,6 +4794,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4813,10 +4813,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117734866</v>
+        <v>117734840</v>
       </c>
       <c r="B42" t="n">
-        <v>97740</v>
+        <v>78219</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4825,25 +4825,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220093</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387512</v>
+        <v>388487</v>
       </c>
       <c r="R42" t="n">
-        <v>6715088</v>
+        <v>6715902</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117743126</v>
+        <v>117743116</v>
       </c>
       <c r="B43" t="n">
-        <v>97857</v>
+        <v>97742</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4931,21 +4931,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>388116</v>
+        <v>387447</v>
       </c>
       <c r="R43" t="n">
-        <v>6715350</v>
+        <v>6715085</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5017,10 +5017,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117743114</v>
+        <v>117743432</v>
       </c>
       <c r="B44" t="n">
-        <v>78480</v>
+        <v>97742</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5029,38 +5029,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ackberget, Vrm</t>
+          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387423</v>
+        <v>387840</v>
       </c>
       <c r="R44" t="n">
-        <v>6715019</v>
+        <v>6715333</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5101,28 +5113,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117743434</v>
+        <v>117743124</v>
       </c>
       <c r="B45" t="n">
-        <v>78480</v>
+        <v>97742</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5131,38 +5144,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
+          <t>Ackberget, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>388196</v>
+        <v>387864</v>
       </c>
       <c r="R45" t="n">
-        <v>6715751</v>
+        <v>6715291</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5209,22 +5222,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117743436</v>
+        <v>117743434</v>
       </c>
       <c r="B46" t="n">
-        <v>97857</v>
+        <v>78482</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5233,25 +5246,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5261,10 +5274,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387837</v>
+        <v>388196</v>
       </c>
       <c r="R46" t="n">
-        <v>6715375</v>
+        <v>6715751</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5323,10 +5336,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117743430</v>
+        <v>117743436</v>
       </c>
       <c r="B47" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5363,10 +5376,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387840</v>
+        <v>387837</v>
       </c>
       <c r="R47" t="n">
-        <v>6715333</v>
+        <v>6715375</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5425,10 +5438,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117743115</v>
+        <v>117743126</v>
       </c>
       <c r="B48" t="n">
-        <v>97740</v>
+        <v>97859</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5441,21 +5454,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5465,10 +5478,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387463</v>
+        <v>388116</v>
       </c>
       <c r="R48" t="n">
-        <v>6715077</v>
+        <v>6715350</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5527,10 +5540,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117743124</v>
+        <v>117743121</v>
       </c>
       <c r="B49" t="n">
-        <v>97740</v>
+        <v>78482</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5539,25 +5552,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5567,10 +5580,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387864</v>
+        <v>387719</v>
       </c>
       <c r="R49" t="n">
-        <v>6715291</v>
+        <v>6715279</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5632,7 +5645,7 @@
         <v>117743120</v>
       </c>
       <c r="B50" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5731,10 +5744,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117743121</v>
+        <v>117743114</v>
       </c>
       <c r="B51" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5771,10 +5784,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>387719</v>
+        <v>387423</v>
       </c>
       <c r="R51" t="n">
-        <v>6715279</v>
+        <v>6715019</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5833,10 +5846,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117743125</v>
+        <v>117743430</v>
       </c>
       <c r="B52" t="n">
-        <v>97740</v>
+        <v>97859</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5849,34 +5862,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ackberget, Vrm</t>
+          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>388061</v>
+        <v>387840</v>
       </c>
       <c r="R52" t="n">
-        <v>6715307</v>
+        <v>6715333</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5923,22 +5936,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117743117</v>
+        <v>117743125</v>
       </c>
       <c r="B53" t="n">
-        <v>78125</v>
+        <v>97742</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5947,25 +5960,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5975,10 +5988,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387578</v>
+        <v>388061</v>
       </c>
       <c r="R53" t="n">
-        <v>6715145</v>
+        <v>6715307</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6037,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117743116</v>
+        <v>117743117</v>
       </c>
       <c r="B54" t="n">
-        <v>97740</v>
+        <v>78127</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6049,25 +6062,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220093</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6077,10 +6090,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387447</v>
+        <v>387578</v>
       </c>
       <c r="R54" t="n">
-        <v>6715085</v>
+        <v>6715145</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6139,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117743119</v>
+        <v>117743115</v>
       </c>
       <c r="B55" t="n">
-        <v>97857</v>
+        <v>97742</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6155,21 +6168,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6179,10 +6192,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387713</v>
+        <v>387463</v>
       </c>
       <c r="R55" t="n">
-        <v>6715228</v>
+        <v>6715077</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6241,10 +6254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117743432</v>
+        <v>117743123</v>
       </c>
       <c r="B56" t="n">
-        <v>97740</v>
+        <v>97859</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6257,46 +6270,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ackberget, Ljusnetjärnarna, Vrm</t>
+          <t>Ackberget, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387840</v>
+        <v>387825</v>
       </c>
       <c r="R56" t="n">
-        <v>6715333</v>
+        <v>6715329</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6337,19 +6338,18 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6359,7 +6359,7 @@
         <v>117743134</v>
       </c>
       <c r="B57" t="n">
-        <v>97740</v>
+        <v>97742</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117743118</v>
+        <v>117743119</v>
       </c>
       <c r="B58" t="n">
-        <v>78480</v>
+        <v>97859</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6470,25 +6470,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>387669</v>
+        <v>387713</v>
       </c>
       <c r="R58" t="n">
-        <v>6715247</v>
+        <v>6715228</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6560,10 +6560,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117743123</v>
+        <v>117743118</v>
       </c>
       <c r="B59" t="n">
-        <v>97857</v>
+        <v>78482</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6572,25 +6572,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>387825</v>
+        <v>387669</v>
       </c>
       <c r="R59" t="n">
-        <v>6715329</v>
+        <v>6715247</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 27265-2020 artfynd.xlsx
+++ b/artfynd/A 27265-2020 artfynd.xlsx
@@ -4302,10 +4302,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117734838</v>
+        <v>117734868</v>
       </c>
       <c r="B37" t="n">
-        <v>86818</v>
+        <v>78516</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>388524</v>
+        <v>387438</v>
       </c>
       <c r="R37" t="n">
-        <v>6715944</v>
+        <v>6715052</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117734868</v>
+        <v>117734838</v>
       </c>
       <c r="B38" t="n">
-        <v>78516</v>
+        <v>86818</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4420,21 +4420,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387438</v>
+        <v>388524</v>
       </c>
       <c r="R38" t="n">
-        <v>6715052</v>
+        <v>6715944</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
